--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314227</v>
+        <v>121314228</v>
       </c>
       <c r="B3" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585154</v>
+        <v>585186</v>
       </c>
       <c r="R3" t="n">
-        <v>6346076</v>
+        <v>6346129</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121314228</v>
+        <v>121314227</v>
       </c>
       <c r="B4" t="n">
-        <v>94844</v>
+        <v>94854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585186</v>
+        <v>585154</v>
       </c>
       <c r="R4" t="n">
-        <v>6346129</v>
+        <v>6346076</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314228</v>
+        <v>121314227</v>
       </c>
       <c r="B3" t="n">
         <v>94854</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585186</v>
+        <v>585154</v>
       </c>
       <c r="R3" t="n">
-        <v>6346129</v>
+        <v>6346076</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121314227</v>
+        <v>121314228</v>
       </c>
       <c r="B4" t="n">
         <v>94854</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585154</v>
+        <v>585186</v>
       </c>
       <c r="R4" t="n">
-        <v>6346076</v>
+        <v>6346129</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314227</v>
+        <v>121314228</v>
       </c>
       <c r="B3" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585154</v>
+        <v>585186</v>
       </c>
       <c r="R3" t="n">
-        <v>6346076</v>
+        <v>6346129</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121314228</v>
+        <v>121314227</v>
       </c>
       <c r="B4" t="n">
-        <v>94854</v>
+        <v>94866</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585186</v>
+        <v>585154</v>
       </c>
       <c r="R4" t="n">
-        <v>6346129</v>
+        <v>6346076</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>121314228</v>
       </c>
       <c r="B3" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>121314227</v>
       </c>
       <c r="B4" t="n">
-        <v>94866</v>
+        <v>94867</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121249539</v>
       </c>
       <c r="B2" t="n">
-        <v>6263</v>
+        <v>6266</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>121314228</v>
       </c>
       <c r="B3" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>121314227</v>
       </c>
       <c r="B4" t="n">
-        <v>94867</v>
+        <v>94870</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121314228</v>
+        <v>121314227</v>
       </c>
       <c r="B3" t="n">
         <v>94870</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585186</v>
+        <v>585154</v>
       </c>
       <c r="R3" t="n">
-        <v>6346129</v>
+        <v>6346076</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -894,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121314227</v>
+        <v>121314228</v>
       </c>
       <c r="B4" t="n">
         <v>94870</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585154</v>
+        <v>585186</v>
       </c>
       <c r="R4" t="n">
-        <v>6346076</v>
+        <v>6346129</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>121314227</v>
       </c>
       <c r="B3" t="n">
-        <v>94870</v>
+        <v>94876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>121314228</v>
       </c>
       <c r="B4" t="n">
-        <v>94870</v>
+        <v>94876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>121314227</v>
       </c>
       <c r="B3" t="n">
-        <v>94876</v>
+        <v>94877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>121314228</v>
       </c>
       <c r="B4" t="n">
-        <v>94876</v>
+        <v>94877</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Henriksson, Marcus Arnesson</t>
+          <t>Marcus Arnesson, Jan Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121249539</v>
+        <v>121314227</v>
       </c>
       <c r="B2" t="n">
-        <v>6266</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105336</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nära Scania, Sm</t>
+          <t>Oskarshamn, nära Scania väster om E22:an, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585199</v>
+        <v>585154</v>
       </c>
       <c r="R2" t="n">
-        <v>6346089</v>
+        <v>6346076</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I tallåga med timmerticka</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,7 +754,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marcus Arnesson, Jan Henriksson</t>
+          <t>Jan Henriksson, Marcus Arnesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +775,7 @@
         <v>121314228</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121314227</v>
+        <v>121249539</v>
       </c>
       <c r="B4" t="n">
-        <v>94885</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,37 +880,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>105336</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Oskarshamn, nära Scania väster om E22:an, Sm</t>
+          <t>Nära Scania, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585154</v>
+        <v>585199</v>
       </c>
       <c r="R4" t="n">
-        <v>6346076</v>
+        <v>6346089</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,6 +949,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I tallåga med timmerticka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,6 +962,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43442-2024 artfynd.xlsx
+++ b/artfynd/A 43442-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121314227</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121314228</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121249539</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>